--- a/Sheets/ShopData.xlsx
+++ b/Sheets/ShopData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76298AEF-B693-4C0C-AD27-240466A1F98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9814FD-BD59-4F78-A4B5-AC4F23C66679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>$$ShopData$$</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,6 +105,10 @@
   </si>
   <si>
     <t>$DisplayName$</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SeedShop_Closed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -768,9 +772,8 @@
       <c r="F5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="5" t="str">
-        <f>A5&amp;"_ClosedMessage"</f>
-        <v>SeedShop_ClosedMessage</v>
+      <c r="G5" t="s">
+        <v>17</v>
       </c>
       <c r="H5" t="s">
         <v>5</v>
@@ -802,9 +805,8 @@
       <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="5" t="str">
-        <f>A6&amp;"_ClosedMessage"</f>
-        <v>VegeShop_ClosedMessage</v>
+      <c r="G6" t="s">
+        <v>17</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>

--- a/Sheets/ShopData.xlsx
+++ b/Sheets/ShopData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tfdkg\UnityProject\Farm\Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9814FD-BD59-4F78-A4B5-AC4F23C66679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6B2586-DB43-4877-9F3A-942D1A592A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{62B5C00F-698F-4EE8-88B3-1AC2C87E7411}"/>
   </bookViews>
   <sheets>
     <sheet name="ShopData" sheetId="6" r:id="rId1"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Seed,Resource</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>$ClosedMessage$</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,6 +105,10 @@
   </si>
   <si>
     <t>SeedShop_Closed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seed,Resource,Animal Product,Artisan Goods,Recipe</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -637,8 +637,8 @@
     <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="30.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.25" bestFit="1" customWidth="1"/>
@@ -710,22 +710,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>3</v>
@@ -761,7 +761,7 @@
         <v>SeedShop_Name</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5">
         <v>10</v>
@@ -770,13 +770,13 @@
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
         <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>5</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -787,14 +787,14 @@
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="str">
         <f>A6&amp;"_Name"</f>
         <v>VegeShop_Name</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5">
         <v>9</v>
@@ -803,13 +803,13 @@
         <v>15</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
         <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
